--- a/ObjectRepository/CDS_ObjectRepository.xlsx
+++ b/ObjectRepository/CDS_ObjectRepository.xlsx
@@ -1550,7 +1550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C385"/>
+  <dimension ref="A1:C386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -8100,6 +8100,23 @@
       <c r="C385" s="2" t="inlineStr">
         <is>
           <t>(//*[@id="[object Object]"])[2]</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/StudyFacet/PHS_Accession/phs003163_Chkbx</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>phs003163_Chkbx</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_PHS Accession_phs003163"]</t>
         </is>
       </c>
     </row>

--- a/ObjectRepository/CDS_ObjectRepository.xlsx
+++ b/ObjectRepository/CDS_ObjectRepository.xlsx
@@ -1550,7 +1550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C386"/>
+  <dimension ref="A1:C388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -8117,6 +8117,40 @@
       <c r="C386" t="inlineStr">
         <is>
           <t>//*[@id="checkbox_PHS Accession_phs003163"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/DiagnosisFacet/PrimaryDiagnosis/LymphomaNOS_Chkbx</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>LymphomaNOS_Chkbx</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_PRIMARY DIAGNOSIS_Lymphoma, NOS"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/SamplesFacet/SampleType/PrimaryXenograftTissue_Chkbx</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>PrimaryXenograftTissue_Chkbx</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_sample type_Primary Xenograft Tissue"]</t>
         </is>
       </c>
     </row>

--- a/ObjectRepository/CDS_ObjectRepository.xlsx
+++ b/ObjectRepository/CDS_ObjectRepository.xlsx
@@ -1550,7 +1550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C388"/>
+  <dimension ref="A1:C406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -8151,6 +8151,312 @@
       <c r="C388" t="inlineStr">
         <is>
           <t>//*[@id="checkbox_sample type_Primary Xenograft Tissue"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/DiagnosisFacet/PrimaryDiagnosis/AbdominalFibromatosis2_Chkbx</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>AbdominalFibromatosis2_Chkbx</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_PRIMARY DIAGNOSIS_Abdominal Fibromatosis"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/DiagnosisFacet/PrimaryDiagnosis/AcuteMyeloidLeukemiaMDS_Chkbx</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>AcuteMyeloidLeukemiaMDS_Chkbx</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_PRIMARY DIAGNOSIS_Acute Myeloid Leukemia With Myelodysplasia-Related Changes"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/DiagnosisFacet/PrimaryDiagnosis/ClearCellCarcinoma2_Chkbx</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>ClearCellCarcinoma2_Chkbx</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_PRIMARY DIAGNOSIS_Clear Cell Carcinoma"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/DiagnosisFacet/PrimaryDiagnosis/LungCancer2_Chkbx</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>LungCancer2_Chkbx</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_PRIMARY DIAGNOSIS_Lung Cancer"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/DiagnosisFacet/PrimaryDiagnosis/MelanomaNOS2_Chkbx</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>MelanomaNOS2_Chkbx</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_PRIMARY DIAGNOSIS_Melanoma, NOS"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/DiagnosisFacet/PrimaryDiagnosis/NeoplasmNOS2_Chkbx</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>NeoplasmNOS2_Chkbx</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_PRIMARY DIAGNOSIS_Neoplasm, NOS"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/DiagnosisFacet/PrimaryDiagnosis/NotReported2_Chkbx</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>NotReported2_Chkbx</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_PRIMARY DIAGNOSIS_Not Reported"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/DiagnosisFacet/PrimaryDiagnosis/ProstateCancer2_Chkbx</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>ProstateCancer2_Chkbx</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_PRIMARY DIAGNOSIS_Prostate Cancer"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/DiagnosisFacet/PrimaryDiagnosis/SarcomaNOS2_Chkbx</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>SarcomaNOS2_Chkbx</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_PRIMARY DIAGNOSIS_Sarcoma, NOS"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/SamplesFacet/SampleType/Analyte2_Chkbx</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Analyte2_Chkbx</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_sample type_Analyte"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/SamplesFacet/SampleType/BloodClot2_Chkbx</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>BloodClot2_Chkbx</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_sample type_Blood Clot"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/SamplesFacet/SampleType/BloodDerivedCancerBoneMarrow_Chkbx</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>BloodDerivedCancerBoneMarrow_Chkbx</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_sample type_Blood Derived Cancer - Bone Marrow"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/SamplesFacet/SampleType/Metastatic2_Chkbx</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Metastatic2_Chkbx</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_sample type_Metastatic"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/SamplesFacet/SampleType/NotSpecifiedinData2_Chkbx</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>NotSpecifiedinData2_Chkbx</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_sample type_Not specified in data"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/SamplesFacet/SampleType/SkinNOS_Chkbx</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>SkinNOS_Chkbx</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_sample type_Skin, NOS"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/SamplesFacet/SampleType/SolidTissueNormal2_Chkbx</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>SolidTissueNormal2_Chkbx</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_sample type_Solid Tissue Normal"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/SamplesFacet/SampleType/Thymus2_Chkbx</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Thymus2_Chkbx</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_sample type_Thymus"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/GenomicFacet/LibrarySource/GenomicDNA_Chkbx</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>GenomicDNA_Chkbx</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_Library Source Material_Genomic DNA"]</t>
         </is>
       </c>
     </row>

--- a/ObjectRepository/CDS_ObjectRepository.xlsx
+++ b/ObjectRepository/CDS_ObjectRepository.xlsx
@@ -1550,7 +1550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C406"/>
+  <dimension ref="A1:C416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -8457,6 +8457,176 @@
       <c r="C406" t="inlineStr">
         <is>
           <t>//*[@id="checkbox_Library Source Material_Genomic DNA"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/GenomicFacet/Platform/Not Applicable_Chkbx</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Not Applicable_Chkbx</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_Platform_Not Applicable"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/GenomicFacet/LibrarySource/Not Applicable_Chkbx</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Not Applicable_Chkbx</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_Library Source Molecule_Not Applicable"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/GenomicFacet/LibraryLayout/Not Applicable_Chkbx</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Not Applicable_Chkbx</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_Library Layout_Not Applicable"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/GenomicFacet/InstrumentModel/Not Applicable_Chkbx</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Not Applicable_Chkbx</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_Instrument Model_Not Applicable"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/StudyFacet/StudyDataTypes/Image Annotation_Chkbx</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Image Annotation_Chkbx</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_Study Data Types_Image Annotation"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/DiagnosisFacet/PrimaryDiagnosis/Neurofibromatosis, NOS_Chkbx</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Neurofibromatosis, NOS_Chkbx</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_PRIMARY DIAGNOSIS_Neurofibromatosis, NOS"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/FilesFacet/FileType/MAF-Chkbx</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>MAF-Chkbx</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_File Type_MAF"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/GenomicFacet/LibraryStrategy/AMPLICON_Chkbx</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>AMPLICON_Chkbx</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_Library Strategy_AMPLICON"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/GenomicFacet/InstrumentModel/Illumina NextSeq 500_Chkbx</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Illumina NextSeq 500_Chkbx</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_Instrument Model_Illumina NextSeq 500"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>CDS/Data_page/Filter/GenomicFacet/InstrumentModel/Illumina HiSeq 4000_Chkbx</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Illumina HiSeq 4000_Chkbx</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>//*[@id="checkbox_instrument model_Illumina HiSeq 4000"]</t>
         </is>
       </c>
     </row>
